--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/INDIANA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/INDIANA_2012.xlsx
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C157">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C620">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C701">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C702">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C732">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1052">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1199">
